--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2021_antofagasta_evolucion.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2021_antofagasta_evolucion.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Acumulado_desde_2018" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Acumulado_desde_2018'!$A$1:$C$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Acumulado_desde_2018'!$A$1:$C$97</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -34,7 +34,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:13</t>
+    <t xml:space="preserve">2026-09-29 14:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -519,8 +519,32 @@
         <v>-15.03</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>-7.15</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>-9.26</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>-9.09</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B4"/>
+  <autoFilter ref="A1:B7"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -1146,8 +1170,536 @@
         <v>-19.06</v>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>-24.96</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>-35.25</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B52" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>-12.87</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B53" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>27.96</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B54" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>27.87</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B55" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>23.42</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B56" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>30.53</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B57" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>11.64</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B58" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>33.47</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B59" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>30.83</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B60" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>4.68</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B61" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>12.38</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B62" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>-27.93</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B63" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>40.42</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B64" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>-14.54</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B65" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>3.84</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B66" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>-31.35</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B67" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>-45.53</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B68" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>-15.33</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B69" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>33.73</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B70" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>33.12</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B71" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>28.99</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B72" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v>41.36</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B73" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v>13.47</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B74" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v>42.28</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B75" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>39.37</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B76" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v>8.67</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B77" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v>13.88</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B78" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C78" s="2" t="n">
+        <v>-35.9</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B79" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C79" s="2" t="n">
+        <v>51.81</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B80" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v>-24.26</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B81" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v>15.53</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B82" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C82" s="2" t="n">
+        <v>-37.23</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B83" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C83" s="2" t="n">
+        <v>-55.93</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B84" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C84" s="2" t="n">
+        <v>-18.92</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B85" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v>40.34</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B86" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C86" s="2" t="n">
+        <v>36.9</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B87" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C87" s="2" t="n">
+        <v>32.72</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B88" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C88" s="2" t="n">
+        <v>48.57</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B89" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C89" s="2" t="n">
+        <v>15.42</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B90" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C90" s="2" t="n">
+        <v>50.04</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B91" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C91" s="2" t="n">
+        <v>46.58</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B92" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C92" s="2" t="n">
+        <v>10.16</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B93" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C93" s="2" t="n">
+        <v>13.98</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B94" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C94" s="2" t="n">
+        <v>-42.31</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B95" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C95" s="2" t="n">
+        <v>60.08</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B96" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C96" s="2" t="n">
+        <v>-29.53</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B97" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C97" s="2" t="n">
+        <v>26.54</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C49"/>
+  <autoFilter ref="A1:C97"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2021_antofagasta_evolucion.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2021_antofagasta_evolucion.xlsx
@@ -34,7 +34,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 14:11</t>
+    <t xml:space="preserve">2026-09-29 18:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2021_antofagasta_evolucion.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2021_antofagasta_evolucion.xlsx
@@ -34,7 +34,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 18:40</t>
+    <t xml:space="preserve">2026-10-05 04:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
